--- a/models/sovereigns/Turkey_Sovereign_Model.xlsx
+++ b/models/sovereigns/Turkey_Sovereign_Model.xlsx
@@ -724,16 +724,34 @@
           <t>real_gdp_growth_pct</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
+      <c r="B6" s="2" t="n">
+        <v>3.4</v>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -931,16 +949,34 @@
           <t>fdi_net_pct_gdp</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>0.8120000000000001</v>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1000,16 +1036,34 @@
           <t>import_cover_months</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
+      <c r="B18" s="2" t="n">
+        <v>5.128</v>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>months</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1104,16 +1158,34 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>1640.223</v>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/models/sovereigns/Turkey_Sovereign_Model.xlsx
+++ b/models/sovereigns/Turkey_Sovereign_Model.xlsx
@@ -652,19 +652,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TCMB</t>
+          <t>TCMB MPC decision (1-week repo auction rate)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sep-26</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1-week repo; definition of 37% (repo vs overnight lending) was an open item</t>
-        </is>
-      </c>
+          <t>10-Sep-26</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -672,15 +668,29 @@
           <t>inflation_expectation_12m_pct</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
+      <c r="B4" s="2" t="n">
+        <v>24.5</v>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sep-26</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TCMB Survey of Market Participants (document states tracking ~24-25%; midpoint)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30-Sep-26</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -712,11 +722,7 @@
           <t>03-Oct-26</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>core CPI-C 28.70%</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -801,7 +807,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>central government</t>
+          <t>central government gross debt</t>
         </is>
       </c>
     </row>
@@ -838,12 +844,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FY26E</t>
+          <t>2026E</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HMB</t>
+          <t>HMB (central government budget deficit, approximate)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -851,11 +857,7 @@
           <t>Aug-26</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>central government budget, tracking</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -924,24 +926,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FY26E</t>
+          <t>2026E</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TCMB</t>
+          <t>HMB / IMF (FY26 projected deficit 2.6% to 2.8% of GDP; midpoint)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jul-26</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>projected 2.6-2.8% deficit; Jul-26 monthly surplus $36M</t>
-        </is>
-      </c>
+          <t>Aug-26</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -999,7 +997,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TCMB</t>
+          <t>TCMB Weekly International Reserves and Foreign Currency Liquidity</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1009,7 +1007,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>FX reserves ex gold; total gross incl. gold $174.4B at 18-Sep-26 (run 2026-10-07_2235)</t>
+          <t>gross FX reserves (as reported by TCMB; gold treatment not stated)</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1084,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TCMB</t>
+          <t>TCMB Short Term External Debt Statistics</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1096,7 +1094,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>remaining maturity, all sectors</t>
+          <t>by remaining maturity, all sectors</t>
         </is>
       </c>
     </row>
@@ -1116,22 +1114,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>Q2-26</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>HMB Gross External Debt Stock Statistics</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>30-Jun-26</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>HMB</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>30-Jun-26</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>gross external debt stock $539.0B</t>
+          <t>gross external debt, all sectors</t>
         </is>
       </c>
     </row>
@@ -1141,16 +1139,34 @@
           <t>gefr_usd_bn</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n"/>
+      <c r="B21" s="2" t="n">
+        <v>208</v>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>next 12m from Jun-26</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>TCMB / HMB</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Jun-26</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>CA deficit + external amortisation due in 12m</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1347,11 +1363,6 @@
       <c r="A33" t="inlineStr">
         <is>
           <t>IMF</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>None (Article IV)</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1436,11 @@
       <c r="B5" s="2" t="n">
         <v>-2.7</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>HMB / IMF, Aug-26</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1436,7 +1451,11 @@
       <c r="B6" s="2" t="n">
         <v>-5.2</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>HMB, Aug-26</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/models/sovereigns/Turkey_Sovereign_Model.xlsx
+++ b/models/sovereigns/Turkey_Sovereign_Model.xlsx
@@ -652,12 +652,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TCMB MPC decision (1-week repo auction rate)</t>
+          <t>TCMB MPC decision, 1-week repo rate (IMF series shows 35.5%, definition unconfirmed)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -683,12 +683,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TCMB Survey of Market Participants (document states tracking ~24-25%; midpoint)</t>
+          <t>TCMB Survey of Market Participants (midpoint of stated 24-25%)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -714,7 +714,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TurkStat</t>
+          <t>TurkStat, Consumer Price Index September 2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF WEO</t>
+          <t>IMF WEO 2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -753,11 +753,7 @@
           <t>08-Oct-26</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -807,7 +803,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>central government gross debt</t>
+          <t>central government debt</t>
         </is>
       </c>
     </row>
@@ -844,12 +840,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>FY26 tracking (approximate)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HMB (central government budget deficit, approximate)</t>
+          <t>HMB budget execution</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -926,17 +922,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>2026F (projected range -2.6 to -2.8)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HMB / IMF (FY26 projected deficit 2.6% to 2.8% of GDP; midpoint)</t>
+          <t>TCMB, HMB projection</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aug-26</t>
+          <t>Jul-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -948,7 +944,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -967,14 +963,10 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -983,7 +975,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>61.56</v>
+        <v>174.4</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -992,22 +984,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>25-Sep-26</t>
+          <t>18-Sep-26</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TCMB Weekly International Reserves and Foreign Currency Liquidity</t>
+          <t>TCMB via run 2026-10-07_2235</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-Sep-26</t>
+          <t>18-Sep-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross FX reserves (as reported by TCMB; gold treatment not stated)</t>
+          <t>gross incl. gold</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1106,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Q2-26</t>
+          <t>30-Jun-26</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1129,7 +1121,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>gross external debt, all sectors</t>
+          <t>gross external debt $539.0B, all sectors</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1146,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TCMB / HMB</t>
+          <t>TCMB/HMB (components not in hand)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1175,7 +1167,7 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1640.223</v>
+        <v>1640.2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1189,7 +1181,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IMF WEO</t>
+          <t>IMF WEO 2026</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1197,11 +1189,7 @@
           <t>08-Oct-26</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1406,8 +1394,14 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="B2" s="2" t="n">
+        <v>1640.2</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IMF WEO 2026, 08-Oct-26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1415,8 +1409,14 @@
           <t>real_gdp_growth_pct</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="B3" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>IMF WEO 2026, 08-Oct-26</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HMB / IMF, Aug-26</t>
+          <t>TCMB/HMB projection range -2.6 to -2.8, midpoint shown, Jul-26</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HMB, Aug-26</t>
+          <t>HMB budget execution, approximate FY26 tracking, Aug-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Turkey_Sovereign_Model.xlsx
+++ b/models/sovereigns/Turkey_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/turkey.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/turkey.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Turkey_Sovereign_Model.xlsx
+++ b/models/sovereigns/Turkey_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 08-Oct-26</t>
+          <t>as of 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TCMB MPC decision, 1-week repo rate (IMF series shows 35.5%, definition unconfirmed)</t>
+          <t>TCMB MPC decision (1-week repo)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TCMB Survey of Market Participants (midpoint of stated 24-25%)</t>
+          <t>TCMB Survey of Market Participants</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -922,12 +922,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026F (projected range -2.6 to -2.8)</t>
+          <t>2026E</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TCMB, HMB projection</t>
+          <t>TCMB, projection of 2.6% to 2.8% deficit (midpoint)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TCMB/HMB (components not in hand)</t>
+          <t>TCMB/HMB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IMF WEO 2026, 08-Oct-26</t>
+          <t>IMF WEO 2026, 2026</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IMF WEO 2026, 08-Oct-26</t>
+          <t>IMF WEO 2026, 2026</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Turkey_Sovereign_Model.xlsx
+++ b/models/sovereigns/Turkey_Sovereign_Model.xlsx
@@ -652,12 +652,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TCMB MPC decision (1-week repo)</t>
+          <t>TCMB MPC decision (1-week repo); IMF series shows 35.5%, definition unconfirmed</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -683,12 +683,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TCMB Survey of Market Participants</t>
+          <t>TCMB Survey of Market Participants (midpoint of stated 24-25%)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -840,17 +840,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FY26 tracking (approximate)</t>
+          <t>2026E</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HMB budget execution</t>
+          <t>HMB, central government budget deficit tracking approx. 5.2% of GDP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aug-26</t>
+          <t>31-Aug-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -927,12 +927,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TCMB, projection of 2.6% to 2.8% deficit (midpoint)</t>
+          <t>TCMB, midpoint of projected 2.6% to 2.8% deficit</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jul-26</t>
+          <t>31-Jul-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -963,7 +963,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>31-Dec-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TCMB/HMB</t>
+          <t>TCMB/HMB (components not in hand)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>30-Jun-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IMF WEO 2026, 2026</t>
+          <t>IMF WEO 2026, 08-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IMF WEO 2026, 2026</t>
+          <t>IMF WEO 2026, 08-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HMB budget execution, approximate FY26 tracking, Aug-26</t>
+          <t>HMB, Aug-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Turkey_Sovereign_Model.xlsx
+++ b/models/sovereigns/Turkey_Sovereign_Model.xlsx
@@ -652,12 +652,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TCMB MPC decision (1-week repo); IMF series shows 35.5%, definition unconfirmed</t>
+          <t>TCMB MPC decision, 1-week repo rate (IMF series shows 35.5%, definition unconfirmed)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -688,7 +688,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -840,17 +840,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>FY26 tracking (approximate)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HMB, central government budget deficit tracking approx. 5.2% of GDP</t>
+          <t>HMB, central government budget</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>31-Aug-26</t>
+          <t>Aug-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -927,12 +927,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TCMB, midpoint of projected 2.6% to 2.8% deficit</t>
+          <t>TCMB, FY26 deficit projected at 2.6% to 2.8% of GDP (midpoint)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>31-Jul-26</t>
+          <t>Jul-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -963,7 +963,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>31-Dec-25</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>gross external debt $539.0B, all sectors</t>
+          <t>gross external debt, $539.0B, HMB denominator</t>
         </is>
       </c>
     </row>
@@ -1141,22 +1141,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>next 12m from Jun-26</t>
+          <t>Jun-26</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TCMB/HMB (components not in hand)</t>
+          <t>TCMB/HMB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>30-Jun-26</t>
+          <t>Jun-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CA deficit + external amortisation due in 12m</t>
+          <t>CA deficit + external amortisation due in 12m (approx., next 12 months; components not in hand)</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IMF WEO 2026, 08-Oct-26</t>
+          <t>IMF WEO 2026</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IMF WEO 2026, 08-Oct-26</t>
+          <t>IMF WEO 2026</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TCMB/HMB projection range -2.6 to -2.8, midpoint shown, Jul-26</t>
+          <t>TCMB, Jul-26 (midpoint of 2.6% to 2.8% deficit projection)</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HMB, Aug-26</t>
+          <t>HMB, Aug-26 (approximate FY26 tracking)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Turkey_Sovereign_Model.xlsx
+++ b/models/sovereigns/Turkey_Sovereign_Model.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -688,7 +688,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -845,12 +845,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HMB, central government budget</t>
+          <t>HMB budget execution, Aug-26</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aug-26</t>
+          <t>31-Aug-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -922,17 +922,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>FY26 projected (midpoint of 2.6% to 2.8% deficit)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TCMB, FY26 deficit projected at 2.6% to 2.8% of GDP (midpoint)</t>
+          <t>TCMB, Jul-26</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jul-26</t>
+          <t>31-Jul-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -963,7 +963,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>31-Dec-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>gross external debt, $539.0B, HMB denominator</t>
+          <t>gross external debt $539.0B, all sectors, HMB GDP denominator</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>next 12 months from Jun-26</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>30-Jun-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CA deficit + external amortisation due in 12m (approx., next 12 months; components not in hand)</t>
+          <t>CA deficit + external amortisation due in 12m</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IMF WEO 2026</t>
+          <t>IMF WEO 2026, 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IMF WEO 2026</t>
+          <t>IMF WEO 2026, 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HMB, Aug-26 (approximate FY26 tracking)</t>
+          <t>HMB budget execution Aug-26 (approximate FY26 tracking), 31-Aug-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Turkey_Sovereign_Model.xlsx
+++ b/models/sovereigns/Turkey_Sovereign_Model.xlsx
@@ -652,12 +652,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TCMB MPC decision, 1-week repo rate (IMF series shows 35.5%, definition unconfirmed)</t>
+          <t>TCMB MPC decision, 1-week repo (IMF series shows 35.5%, definition unconfirmed)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -688,7 +688,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -845,12 +845,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HMB budget execution, Aug-26</t>
+          <t>HMB, central government budget execution</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>31-Aug-26</t>
+          <t>Aug-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -922,7 +922,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FY26 projected (midpoint of 2.6% to 2.8% deficit)</t>
+          <t>2026 projection (range -2.6 to -2.8, midpoint)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>31-Jul-26</t>
+          <t>Jul-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -963,7 +963,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>31-Dec-25</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TCMB Short Term External Debt Statistics</t>
+          <t>TCMB, Short Term External Debt Statistics</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HMB Gross External Debt Stock Statistics</t>
+          <t>HMB, Gross External Debt Stock Statistics</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>gross external debt $539.0B, all sectors, HMB GDP denominator</t>
+          <t>gross external debt $539.0B, all sectors</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>next 12 months from Jun-26</t>
+          <t>Jun-26</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>30-Jun-26</t>
+          <t>Jun-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IMF WEO 2026, 09-Oct-26</t>
+          <t>IMF WEO 2026, 08-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IMF WEO 2026, 09-Oct-26</t>
+          <t>IMF WEO 2026, 08-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HMB budget execution Aug-26 (approximate FY26 tracking), 31-Aug-26</t>
+          <t>HMB, Aug-26 (approximate FY26 tracking)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Turkey_Sovereign_Model.xlsx
+++ b/models/sovereigns/Turkey_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/turkey.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/turkey.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Turkey_Sovereign_Model.xlsx
+++ b/models/sovereigns/Turkey_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/turkey.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/turkey.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Turkey_Sovereign_Model.xlsx
+++ b/models/sovereigns/Turkey_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 09-Oct-26</t>
+          <t>as of 19-Oct-26</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TCMB MPC decision, 1-week repo (IMF series shows 35.5%, definition unconfirmed)</t>
+          <t>TCMB 1-week repo rate</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>Sep-26 survey</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TCMB Survey of Market Participants (midpoint of stated 24-25%)</t>
+          <t>TCMB market participants survey</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TurkStat, Consumer Price Index September 2026</t>
+          <t>TurkStat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF WEO 2026</t>
+          <t>Fitch forecast via Voice of Emirates</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>18-Jul-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -845,7 +845,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HMB, central government budget execution</t>
+          <t>HMB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>World Bank WDI</t>
+          <t>World Bank WDI (FDI liabilities)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>174.4</v>
+        <v>167.4</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -984,22 +984,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18-Sep-26</t>
+          <t>week to 02-Oct-26</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TCMB via run 2026-10-07_2235</t>
+          <t>TCMB via Türkiye Today</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>18-Sep-26</t>
+          <t>02-Oct-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross incl. gold</t>
+          <t>gross incl. gold (FX USD 60.3bn, gold USD 107.1bn)</t>
         </is>
       </c>
     </row>
@@ -1009,16 +1009,34 @@
           <t>net_reserves_usd_bn</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n"/>
+      <c r="B17" s="2" t="n">
+        <v>137.1</v>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Aug-26</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>IMF International Liquidity and reserve template</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Aug-26</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>gross net of predetermined 1y drains (IMF template); not net ex swaps</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1076,7 +1094,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TCMB, Short Term External Debt Statistics</t>
+          <t>TCMB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1086,7 +1104,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>by remaining maturity, all sectors</t>
+          <t>by remaining maturity</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1129,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HMB, Gross External Debt Stock Statistics</t>
+          <t>HMB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1121,7 +1139,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>gross external debt $539.0B, all sectors</t>
+          <t>gross external debt USD 539.0bn</t>
         </is>
       </c>
     </row>
@@ -1410,11 +1428,11 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IMF WEO 2026, 08-Oct-26</t>
+          <t>Fitch via Voice of Emirates, 18-Jul-26</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1471,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HMB, Aug-26 (approximate FY26 tracking)</t>
+          <t>HMB, Aug-26 (approximate)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Turkey_Sovereign_Model.xlsx
+++ b/models/sovereigns/Turkey_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/turkey.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/turkey.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Turkey_Sovereign_Model.xlsx
+++ b/models/sovereigns/Turkey_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 19-Oct-26</t>
+          <t>as of 27-Oct-26</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/turkey.json</t>
+          <t>built 27-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/turkey.json</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -647,17 +647,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>Oct-26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TCMB 1-week repo rate</t>
+          <t>TCMB one-week repo rate via Hürriyet Daily News</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>22-Oct-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>24.5</v>
+        <v>23.89</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -678,17 +678,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sep-26 survey</t>
+          <t>Oct-26</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TCMB market participants survey</t>
+          <t>TCMB market participants survey via Hürriyet Daily News (date unconfirmed)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>Oct-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -740,12 +740,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>2026F</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fitch forecast via Voice of Emirates</t>
+          <t>Fitch projection via Hürriyet Daily News</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HMB</t>
+          <t>HMB (Ministry of Treasury and Finance)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -840,12 +840,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FY26 tracking (approximate)</t>
+          <t>2026E</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HMB</t>
+          <t>HMB (FY26 deficit tracking about 5.2% of GDP)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>167.4</v>
+        <v>171.6</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -984,22 +984,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>week to 02-Oct-26</t>
+          <t>15-Oct-26</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TCMB via Türkiye Today</t>
+          <t>TCMB weekly data via web search summary</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>02-Oct-26</t>
+          <t>15-Oct-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross incl. gold (FX USD 60.3bn, gold USD 107.1bn)</t>
+          <t>gross incl. gold (search summary of TCMB weekly data, Medium-Low confidence, unconfirmed against TCMB release)</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>gross net of predetermined 1y drains (IMF template); not net ex swaps</t>
+          <t>gross reserves net of predetermined 1y drains (IMF international liquidity template); not net ex swaps and banks' FX required reserves</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HMB</t>
+          <t>HMB (Ministry of Treasury and Finance)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>gross external debt USD 539.0bn</t>
+          <t>gross external debt (USD 539.0bn) as % of GDP</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CA deficit + external amortisation due in 12m</t>
+          <t>CA deficit + external amortisation due in 12m (approximate)</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fitch via Voice of Emirates, 18-Jul-26</t>
+          <t>Fitch via Hürriyet Daily News, 18-Jul-26</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HMB, Aug-26 (approximate)</t>
+          <t>HMB, Aug-26</t>
         </is>
       </c>
     </row>
@@ -1512,8 +1512,14 @@
           <t>gross_reserves_usd_bn</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="B10" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Fitch projection for end-2026 via Hürriyet Daily News, 18-Jul-26</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
